--- a/templates/template-retro.xlsx
+++ b/templates/template-retro.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -434,8 +434,10 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -461,15 +463,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Errore di stampa</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Tipo di change</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo di errore di stampa</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Retro - Categoria</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Retro - Nome</t>
         </is>

--- a/templates/template-retro.xlsx
+++ b/templates/template-retro.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istruzioni" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,9 +30,30 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00606060"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,11 +62,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A3F6B"/>
+        <fgColor rgb="002F3B52"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3B0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -52,14 +79,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="009AA5B1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -426,21 +466,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Serie</t>
@@ -463,27 +505,323 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Errore di stampa</t>
+          <t>Versione</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Tipo di change</t>
+          <t>Tipologia di change</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Tipo di errore di stampa</t>
+          <t>Tipologia di omaggio</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Retro - Categoria</t>
+          <t>Tipologia di errore di stampa</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Retro - Nome</t>
+          <t>Retro di partenza - Categoria</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Retro di partenza - Sottocategoria</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Retro di partenza - Nome</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Template import Retro — figurinesgorbions.it</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Formato introdotto nella v6.354. Un file con le intestazioni VECCHIE («Tipo di change»,</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>«Errore di stampa», «Retro - Categoria») viene rifiutato con «colonna mancante»: e' voluto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>COME SI USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>1. Compila il foglio «Retro»: riga 1 le intestazioni (non toccarle), una riga per retro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2. Nel sito: Admin -&gt; Foto e import -&gt; Caricamento massivo retro. Scegli la serie, carica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>3. Le righe con Serie diversa da quella selezionata vengono ignorate, non sono un errore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>4. I retro base si importano prima dei loro figli: ci pensa la procedura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>QUESTO FOGLIO NON VIENE LETTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>L'import legge SOLO il primo foglio. Per la stessa ragione nel foglio «Retro» non c'e'</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>nessuna riga d'esempio: in un template da importare diventerebbe un dato vero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>VERSIONE — i quattro valori ammessi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>base  ·  change  ·  omaggio  ·  errore di stampa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Un retro NON puo' essere una variazione: la variazione si distingue nel retro, quindi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>«variazione di un retro» non vuol dire niente. Sono quattro, non sei come per le figurine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>LE COLONNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Colonna</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>A cosa serve</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Serie</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Nome completo della serie. Obbligatoria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Categoria del retro. Obbligatoria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Sottocategoria</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Sottocategoria del retro, se applicabile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nome</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Nome del retro. Obbligatorio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Versione</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Uno dei quattro valori qui sopra. Obbligatoria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Tipologia di change</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Solo con Versione = change, e obbligatoria. Deve essere una delle tipologie configurate sulla serie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Tipologia di omaggio</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Solo con Versione = omaggio, e obbligatoria. Idem — fra quelle dei RETRO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tipologia di errore di stampa</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Solo con Versione = errore di stampa, e obbligatoria. Idem, fra quelle dei RETRO. Dalla v6.354 e' un elenco chiuso: prima era testo libero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Retro di partenza - Categoria</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Il retro da cui questo discende. Obbligatoria per le versioni non base, vietata per la base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Retro di partenza - Sottocategoria</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Facoltativa. Serve quando senza di lei restano piu' candidati: in quel caso la riga viene scartata elencando fra quali scegliere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Retro di partenza - Nome</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Il nome del retro di partenza. Obbligatoria per le versioni non base.</t>
         </is>
       </c>
     </row>
